--- a/pruebas/Gerencia/TALENTO HUMANO.xlsx
+++ b/pruebas/Gerencia/TALENTO HUMANO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ade4bf4107253254/OPAUSTRO DASHBOARD/TI OPAUSTRO/APP OPAUSTRO/APP OPAUSTRO/Gerencia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="8_{13C18F3D-9789-42FE-A96C-D3EBD5B9B8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{996977CD-B87C-4485-A8E4-AA98CA6C457C}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="8_{13C18F3D-9789-42FE-A96C-D3EBD5B9B8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{674EB762-6582-42B0-8157-783A31CCBF6F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TALENTO ACTUAL" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="78">
   <si>
     <t>TALENTO HUMANO - SITUACION ACTUAL POR DEPARTAMENTO</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>Adulteracion de recibo de cobro</t>
+  </si>
+  <si>
+    <t>AGOSTO</t>
   </si>
 </sst>
 </file>
@@ -838,7 +841,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="16">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C4" s="4">
         <v>79</v>
@@ -881,7 +884,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="16">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C5" s="4">
         <v>22</v>
@@ -924,7 +927,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="16">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C6" s="4">
         <v>29</v>
@@ -1020,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1893,6 +1896,120 @@
       </c>
       <c r="K24" s="13">
         <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="11">
+        <v>75</v>
+      </c>
+      <c r="E25" s="11">
+        <v>4</v>
+      </c>
+      <c r="F25" s="11">
+        <v>5</v>
+      </c>
+      <c r="G25" s="11">
+        <v>0</v>
+      </c>
+      <c r="H25" s="11">
+        <v>0</v>
+      </c>
+      <c r="I25" s="13">
+        <f t="shared" ref="I25:I27" si="9">IF(D25=0,0,(E25+F25)/D25)</f>
+        <v>0.12</v>
+      </c>
+      <c r="J25" s="13">
+        <f t="shared" ref="J25:J27" si="10">IF(D25=0,0,E25/D25)</f>
+        <v>5.3333333333333337E-2</v>
+      </c>
+      <c r="K25" s="13">
+        <f t="shared" ref="K25:K27" si="11">IF(D25=0,0,F25/D25)</f>
+        <v>6.6666666666666666E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="11">
+        <v>22</v>
+      </c>
+      <c r="E26" s="11">
+        <v>0</v>
+      </c>
+      <c r="F26" s="11">
+        <v>0</v>
+      </c>
+      <c r="G26" s="11">
+        <v>0</v>
+      </c>
+      <c r="H26" s="11">
+        <v>0</v>
+      </c>
+      <c r="I26" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="13">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="13">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="11">
+        <v>29</v>
+      </c>
+      <c r="E27" s="11">
+        <v>0</v>
+      </c>
+      <c r="F27" s="11">
+        <v>0</v>
+      </c>
+      <c r="G27" s="11">
+        <v>0</v>
+      </c>
+      <c r="H27" s="11">
+        <v>0</v>
+      </c>
+      <c r="I27" s="13">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="13">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="13">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>

--- a/pruebas/Gerencia/TALENTO HUMANO.xlsx
+++ b/pruebas/Gerencia/TALENTO HUMANO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ade4bf4107253254/OPAUSTRO DASHBOARD/TI OPAUSTRO/APP OPAUSTRO/APP OPAUSTRO/Gerencia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ade4bf4107253254/OPAUSTRO DASHBOARD/TI OPAUSTRO/CLAUDE/APP OPAUSTRO/Gerencia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="8_{13C18F3D-9789-42FE-A96C-D3EBD5B9B8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{674EB762-6582-42B0-8157-783A31CCBF6F}"/>
+  <xr:revisionPtr revIDLastSave="106" documentId="8_{13C18F3D-9789-42FE-A96C-D3EBD5B9B8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3B6B811-E96B-4E90-86D4-6CDBDC29D19A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="78">
   <si>
     <t>TALENTO HUMANO - SITUACION ACTUAL POR DEPARTAMENTO</t>
   </si>
@@ -478,15 +478,15 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -767,20 +767,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
     </row>
     <row r="2" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -821,33 +821,33 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="21"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="19"/>
     </row>
     <row r="4" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="16">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C4" s="4">
         <v>79</v>
       </c>
       <c r="D4" s="4">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E4" s="4">
         <v>0</v>
@@ -860,15 +860,15 @@
       </c>
       <c r="H4" s="5">
         <f>C4-D4</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I4" s="6">
         <f>IF(C4=0,0,D4/C4)</f>
-        <v>0.94936708860759489</v>
+        <v>0.97468354430379744</v>
       </c>
       <c r="J4" s="6">
         <f>IF(D4=0,0,(F4+G4)/D4)</f>
-        <v>2.6666666666666668E-2</v>
+        <v>2.5974025974025976E-2</v>
       </c>
       <c r="K4" s="6">
         <f>4%</f>
@@ -884,7 +884,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="16">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C5" s="4">
         <v>22</v>
@@ -927,13 +927,13 @@
         <v>16</v>
       </c>
       <c r="B6" s="16">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C6" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="4">
         <v>2</v>
@@ -972,11 +972,11 @@
       <c r="B7" s="8"/>
       <c r="C7" s="9">
         <f t="shared" ref="C7:H7" si="0">SUM(C4:C6)</f>
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D7" s="9">
         <f t="shared" si="0"/>
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
@@ -992,15 +992,15 @@
       </c>
       <c r="H7" s="9">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I7" s="10">
         <f>IF(C7=0,0,D7/C7)</f>
-        <v>0.96923076923076923</v>
+        <v>0.98473282442748089</v>
       </c>
       <c r="J7" s="10">
         <f>IF(D7=0,0,(F7+G7)/D7)</f>
-        <v>2.3809523809523808E-2</v>
+        <v>2.3255813953488372E-2</v>
       </c>
       <c r="K7" s="10">
         <f>4%</f>
@@ -1023,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1037,19 +1037,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
     </row>
     <row r="2" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1087,19 +1087,19 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="21"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="19"/>
     </row>
     <row r="4" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
@@ -2010,6 +2010,120 @@
       </c>
       <c r="K27" s="13">
         <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="11">
+        <v>77</v>
+      </c>
+      <c r="E28" s="11">
+        <v>4</v>
+      </c>
+      <c r="F28" s="11">
+        <v>2</v>
+      </c>
+      <c r="G28" s="11">
+        <v>0</v>
+      </c>
+      <c r="H28" s="11">
+        <v>0</v>
+      </c>
+      <c r="I28" s="13">
+        <f t="shared" ref="I28:I30" si="12">IF(D28=0,0,(E28+F28)/D28)</f>
+        <v>7.792207792207792E-2</v>
+      </c>
+      <c r="J28" s="13">
+        <f t="shared" ref="J28:J30" si="13">IF(D28=0,0,E28/D28)</f>
+        <v>5.1948051948051951E-2</v>
+      </c>
+      <c r="K28" s="13">
+        <f t="shared" ref="K28:K30" si="14">IF(D28=0,0,F28/D28)</f>
+        <v>2.5974025974025976E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="11">
+        <v>22</v>
+      </c>
+      <c r="E29" s="11">
+        <v>0</v>
+      </c>
+      <c r="F29" s="11">
+        <v>0</v>
+      </c>
+      <c r="G29" s="11">
+        <v>0</v>
+      </c>
+      <c r="H29" s="11">
+        <v>0</v>
+      </c>
+      <c r="I29" s="13">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="13">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="13">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="11">
+        <v>30</v>
+      </c>
+      <c r="E30" s="11">
+        <v>1</v>
+      </c>
+      <c r="F30" s="11">
+        <v>0</v>
+      </c>
+      <c r="G30" s="11">
+        <v>0</v>
+      </c>
+      <c r="H30" s="11">
+        <v>0</v>
+      </c>
+      <c r="I30" s="13">
+        <f t="shared" si="12"/>
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="J30" s="13">
+        <f t="shared" si="13"/>
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="K30" s="13">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -2041,18 +2155,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
     </row>
     <row r="2" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2087,18 +2201,18 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="21"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="19"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
